--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -455,7 +455,7 @@
   </si>
   <si>
     <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 {hasValue() or (children().count() &gt; id.count())}
-ext-1:拡張機能または値[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>ImagingStudy.modifierExtension</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-imagingstudy-endoscopy.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2144" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="452">
   <si>
     <t>Property</t>
   </si>
@@ -1178,7 +1178,10 @@
     <t>このシリーズの対象となる解剖学的部位。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
+    <t>解剖学的位置を記述するコード。左右対称性を含む場合があります。</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -1769,7 +1772,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="28.546875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="35.1484375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="71.15234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -6409,9 +6412,11 @@
       <c r="X40" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="Y40" s="2"/>
+      <c r="Y40" t="s" s="2">
+        <v>371</v>
+      </c>
       <c r="Z40" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6447,10 +6452,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6461,10 +6466,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6490,10 +6495,10 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>265</v>
@@ -6525,10 +6530,10 @@
         <v>283</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6546,7 +6551,7 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6564,10 +6569,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6578,10 +6583,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6604,13 +6609,13 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>265</v>
@@ -6663,7 +6668,7 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6681,10 +6686,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6695,10 +6700,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6724,13 +6729,13 @@
         <v>198</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6780,7 +6785,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6801,7 +6806,7 @@
         <v>203</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6812,14 +6817,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6841,16 +6846,16 @@
         <v>312</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>265</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6899,7 +6904,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6914,13 +6919,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>229</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6931,10 +6936,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7046,10 +7051,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7163,10 +7168,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7282,10 +7287,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7311,16 +7316,16 @@
         <v>262</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>265</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
@@ -7345,13 +7350,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7369,7 +7374,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7401,10 +7406,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7427,13 +7432,13 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>265</v>
@@ -7486,7 +7491,7 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>90</v>
@@ -7504,24 +7509,24 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7547,10 +7552,10 @@
         <v>312</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7601,7 +7606,7 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7619,7 +7624,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7633,10 +7638,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7748,10 +7753,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7865,10 +7870,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7984,14 +7989,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8013,16 +8018,16 @@
         <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
@@ -8035,7 +8040,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8071,7 +8076,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8092,7 +8097,7 @@
         <v>336</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>79</v>
@@ -8103,14 +8108,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8132,13 +8137,13 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8164,11 +8169,11 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8186,7 +8191,7 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>90</v>
@@ -8204,10 +8209,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8218,14 +8223,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8247,13 +8252,13 @@
         <v>241</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8303,7 +8308,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8321,10 +8326,10 @@
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8335,10 +8340,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8364,13 +8369,13 @@
         <v>305</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8420,7 +8425,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8438,10 +8443,10 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
